--- a/procurement-contract-automation/data-model/DECISION_RULES.xlsx
+++ b/procurement-contract-automation/data-model/DECISION_RULES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://people.ey.com/personal/anastasios_kakavoulis_gr_ey_com/Documents/Desktop/Claude Code/Procurement/Vendors' Contracts/LEGAL CONTRACTS/LEGAL CONTRACTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8902977-DD39-4F95-AE84-8C8FDDC2FD20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AEE8239-FF67-4D53-873A-95729B1A73E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BA3AC526-DBB7-4647-9060-C46E6CD173A8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3C22CC59-EE33-46E1-8773-EC40112E9D41}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Μεταβλητές Απόφασης" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="679">
   <si>
     <t>Α/Α</t>
   </si>
@@ -1252,10 +1252,10 @@
     <t>— (εκτός αρίθμησης)</t>
   </si>
   <si>
-    <t>¶60–60</t>
-  </si>
-  <si>
-    <t>Άρθρο 28. ΣΧΕΣΕΙΣ ΜΕΤΑΞΥ ΤΩΝ ΣΥΜΒΑΛΛΟΜΕΝΩΝ41</t>
+    <t>¶10–10</t>
+  </si>
+  <si>
+    <t>μεταξύ</t>
   </si>
   <si>
     <t>B</t>
@@ -1435,6 +1435,12 @@
     <t>Ορόσημα/Παραδοτέα</t>
   </si>
   <si>
+    <t>¶121–121</t>
+  </si>
+  <si>
+    <t>Ποσό … ευρώ (…€) το οποίο αφορά την αμοιβή της Εταιρείας για την παροχή των Υπηρεσιών Υλοποίησης (Professional Services), θα καταβληθεί τμηματικά και εντός σαράντα πέντε …</t>
+  </si>
+  <si>
     <t>¶77–77</t>
   </si>
   <si>
@@ -1552,10 +1558,10 @@
     <t>Ο Ανάδοχος ευθύνεται έναντι της ΕΤΕ, χωρίς κανέναν απολύτως περιορισμό, για όλες τις απαιτήσεις, ζημίες, έξοδα και αποζημιώσεις σε σχέση με το θάνατο και τον τραυματισμό …</t>
   </si>
   <si>
-    <t>¶153–153</t>
-  </si>
-  <si>
-    <t>Η Εταιρεία θα είναι αυτή και μόνο αποκλειστικά υπεύθυνη αστικά και ποινικά, για κάθε τυχόν ατύχημα ή ζημιά, που είναι δυνατόν να προκληθεί κατά την εκτέλεση των Υπηρεσιών…</t>
+    <t>¶132–132</t>
+  </si>
+  <si>
+    <t>¶101–101</t>
   </si>
   <si>
     <t>¶158–166</t>
@@ -1639,10 +1645,10 @@
     <t>Ο Ανάδοχος εγγυάται ότι κατά την Περίοδο Εγγύησης το Σύστημα που παραδίδεται βάσει της παρούσας Σύμβασης:</t>
   </si>
   <si>
-    <t>¶245–245</t>
-  </si>
-  <si>
-    <t>Εγγύηση σχετικά με ιούς</t>
+    <t>¶237–237</t>
+  </si>
+  <si>
+    <t>(γ)θα είναι απαλλαγμένο από οποιοδήποτε πραγματικό ελάττωμα, καθώς και από οποιοδήποτε νομικό ελάττωμα, περιλαμβανομένων, ενδεικτικά, των βαρών, επιβαρύνσεων και εμπράγμα…</t>
   </si>
   <si>
     <t>¶109–109</t>
@@ -1843,6 +1849,15 @@
     <t>Στο πλαίσιο της παρούσας, η Εταιρεία συμφωνείται να χρησιμοποιήσει περιοριστικά τους κάτωθι υπεργολάβους:</t>
   </si>
   <si>
+    <t>ΜΕΡΙΚΩΣ</t>
+  </si>
+  <si>
+    <t>ΜΕΡΙΚΗ ΚΑΛΥΨΗ</t>
+  </si>
+  <si>
+    <t>Η Εταιρεία δεσμεύεται από το επαγγελματικό απόρρητο και υποχρεούται να εξασφαλίζει ότι όλες οι Εμπιστευτικές Πληροφορίες που λαμβάνει από την Τράπεζα στο πλαίσιο του Έργο…</t>
+  </si>
+  <si>
     <t>ΔΙΚΑΙΩΜΑΤΑ ΠΡΟΣΒΑΣΗΣ, ΠΛΗΡΟΦΟΡΗΣΗΣ ΚΑΙ ΕΛΕΓΧΟΥ</t>
   </si>
   <si>
@@ -1918,7 +1933,7 @@
     <t>¶231–231</t>
   </si>
   <si>
-    <t>Κάθε έγγραφο της Τράπεζας προς την Εταιρεία κοινοποιείται στην έδρα της Εταιρείας: Αθήνα, Λ. Μεσογείων 2-4. Κάθε έγγραφο της Εταιρείας προς την Τράπεζα κοινοποιείται στην…</t>
+    <t>Κάθε έγγραφο της Τράπεζας προς την Εταιρεία κοινοποιείται στην έδρα της Εταιρείας, …. Κάθε έγγραφο της Εταιρείας προς την Τράπεζα κοινοποιείται στη …. Σε περίπτωση αλλαγή…</t>
   </si>
   <si>
     <t>ΝΟΜΟΣ ΚΑΙ ΔΙΑΦΟΡΕΣ</t>
@@ -2017,10 +2032,22 @@
     <t>Η παρούσα Σύμβαση δεσμεύει τον Ανάδοχο και την ΕΤΕ και τους αντίστοιχους διαδόχους τους και επιτρεπόμενους εκδοχείς τους.</t>
   </si>
   <si>
+    <t>Σε κάθε περίπτωση που θα συμβεί οποιοδήποτε από τα ανωτέρω (υποκατάσταση, εκχώρηση, μεταβίβαση) μεταξύ της Εταιρείας και του νομικού προσώπου (που θα υποκαταστήσει την Τρ…</t>
+  </si>
+  <si>
     <t>¶419–421</t>
   </si>
   <si>
     <t>Εάν οποιαδήποτε διάταξη της Σύμβασης κριθεί άκυρη ή μη εκτελεστή, η πλήρης Σύμβαση δεν καθίσταται άκυρη ή μη εκτελεστή λόγω του γεγονότος αυτού, αλλά θα ερμηνεύεται ωσάν …</t>
+  </si>
+  <si>
+    <t>Η ακυρότητα ενός ή και περισσοτέρων όρων της παρούσας δεν επιφέρει την ακυρότητα ολόκληρης της Σύμβασης, η οποία, καθ’ ο μέρος είναι έγκυρη, θα εξακολουθήσει να ισχύει υπ…</t>
+  </si>
+  <si>
+    <t>¶227–227</t>
+  </si>
+  <si>
+    <t>Η ακυρότητα ενός ή και περισσοτέρων όρων της παρούσας, δεν επιφέρει την ακυρότητα ολόκληρης της Σύμβασης, η οποία, καθ’ ο μέρος είναι έγκυρη, θα εξακολουθήσει να ισχύει υ…</t>
   </si>
   <si>
     <t>¶417–418</t>
@@ -2637,7 +2664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1A7544C-7F3F-47A8-8E67-7846FB9BEA2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69872C1E-D2A1-4685-A8A8-1DA56A8E5470}">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3162,13 +3189,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{F1A7544C-7F3F-47A8-8E67-7846FB9BEA2D}"/>
+  <autoFilter ref="A1:H1" xr:uid="{69872C1E-D2A1-4685-A8A8-1DA56A8E5470}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5355FE0D-B791-4A82-9A76-EFC59A9A4881}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A83F297-E814-4DBC-A936-3201D298E02A}">
   <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4327,13 +4354,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{5355FE0D-B791-4A82-9A76-EFC59A9A4881}"/>
+  <autoFilter ref="A1:F1" xr:uid="{1A83F297-E814-4DBC-A936-3201D298E02A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400E2627-0F8D-4FC4-A487-CED8B01E3610}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86EC9F80-DD51-4E09-9A18-11ADEB77177F}">
   <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6127,13 +6154,13 @@
       <c r="I65" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{400E2627-0F8D-4FC4-A487-CED8B01E3610}"/>
+  <autoFilter ref="A1:I1" xr:uid="{86EC9F80-DD51-4E09-9A18-11ADEB77177F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{275A6EB1-D5DE-4F87-8745-246DEC97BDFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1C7BA50-F412-48E8-964F-55E1123543BE}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6630,13 +6657,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{275A6EB1-D5DE-4F87-8745-246DEC97BDFC}"/>
+  <autoFilter ref="A1:G1" xr:uid="{C1C7BA50-F412-48E8-964F-55E1123543BE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97AF4AC5-9F13-4DF0-840B-0C580C166032}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C22EEF-9522-413E-AD40-ED5C9924E1A2}">
   <dimension ref="A1:K152"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7576,28 +7603,40 @@
         <v>460</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A28" s="8">
+    <row r="28" spans="1:11" ht="24" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="E28" s="17" t="s">
-        <v>448</v>
-      </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="23"/>
+      <c r="E28" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="G28" s="5">
+        <v>4</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="J28" s="5">
+        <v>1</v>
+      </c>
+      <c r="K28" s="21" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="29" spans="1:11" ht="24" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
@@ -7625,13 +7664,13 @@
         <v>452</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J29" s="2">
         <v>1</v>
       </c>
       <c r="K29" s="22" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -7683,13 +7722,13 @@
         <v>452</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J31" s="2">
         <v>1</v>
       </c>
       <c r="K31" s="22" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -7718,13 +7757,13 @@
         <v>452</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J32" s="5">
         <v>1</v>
       </c>
       <c r="K32" s="21" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -7753,13 +7792,13 @@
         <v>138</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J33" s="2">
         <v>26</v>
       </c>
       <c r="K33" s="22" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -7788,13 +7827,13 @@
         <v>452</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J34" s="5">
         <v>1</v>
       </c>
       <c r="K34" s="21" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -7823,13 +7862,13 @@
         <v>452</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J35" s="2">
         <v>1</v>
       </c>
       <c r="K35" s="22" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -7855,16 +7894,16 @@
         <v>3</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J36" s="5">
         <v>31</v>
       </c>
       <c r="K36" s="21" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -7890,16 +7929,16 @@
         <v>5</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J37" s="2">
         <v>35</v>
       </c>
       <c r="K37" s="22" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -7925,16 +7964,16 @@
         <v>5</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J38" s="5">
         <v>23</v>
       </c>
       <c r="K38" s="21" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -7960,16 +7999,16 @@
         <v>3</v>
       </c>
       <c r="H39" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="J39" s="2">
         <v>1</v>
       </c>
       <c r="K39" s="22" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -7995,16 +8034,16 @@
         <v>5</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="J40" s="5">
         <v>1</v>
       </c>
       <c r="K40" s="21" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8030,16 +8069,16 @@
         <v>5</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J41" s="2">
         <v>1</v>
       </c>
       <c r="K41" s="22" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8065,16 +8104,16 @@
         <v>3</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J42" s="5">
         <v>1</v>
       </c>
       <c r="K42" s="21" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8100,16 +8139,16 @@
         <v>5</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J43" s="2">
         <v>1</v>
       </c>
       <c r="K43" s="22" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8135,16 +8174,16 @@
         <v>5</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J44" s="5">
         <v>1</v>
       </c>
       <c r="K44" s="21" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -8170,16 +8209,16 @@
         <v>3</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -8208,13 +8247,13 @@
         <v>442</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J46" s="5">
         <v>18</v>
       </c>
       <c r="K46" s="21" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -8243,13 +8282,13 @@
         <v>445</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J47" s="2">
         <v>16</v>
       </c>
       <c r="K47" s="22" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8278,13 +8317,13 @@
         <v>151</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J48" s="5">
         <v>5</v>
       </c>
       <c r="K48" s="21" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8313,13 +8352,13 @@
         <v>151</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J49" s="2">
         <v>14</v>
       </c>
       <c r="K49" s="22" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8345,19 +8384,19 @@
         <v>8</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J50" s="5">
         <v>6</v>
       </c>
       <c r="K50" s="21" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="24" x14ac:dyDescent="0.35">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -8380,19 +8419,19 @@
         <v>5</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J51" s="2">
         <v>1</v>
       </c>
       <c r="K51" s="22" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="24" x14ac:dyDescent="0.35">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -8415,16 +8454,16 @@
         <v>5</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="J52" s="5">
         <v>1</v>
       </c>
       <c r="K52" s="21" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8453,13 +8492,13 @@
         <v>157</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J53" s="2">
         <v>9</v>
       </c>
       <c r="K53" s="22" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8488,13 +8527,13 @@
         <v>159</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J54" s="5">
         <v>9</v>
       </c>
       <c r="K54" s="21" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8520,16 +8559,16 @@
         <v>13</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J55" s="2">
         <v>17</v>
       </c>
       <c r="K55" s="22" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8555,16 +8594,16 @@
         <v>8</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J56" s="5">
         <v>36</v>
       </c>
       <c r="K56" s="21" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8590,16 +8629,16 @@
         <v>8</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J57" s="2">
         <v>5</v>
       </c>
       <c r="K57" s="22" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8625,16 +8664,16 @@
         <v>13</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J58" s="5">
         <v>1</v>
       </c>
       <c r="K58" s="21" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8660,16 +8699,16 @@
         <v>8</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J59" s="2">
         <v>1</v>
       </c>
       <c r="K59" s="22" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8695,16 +8734,16 @@
         <v>5</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J60" s="5">
         <v>1</v>
       </c>
       <c r="K60" s="21" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8730,16 +8769,16 @@
         <v>13</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J61" s="2">
         <v>1</v>
       </c>
       <c r="K61" s="22" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8765,16 +8804,16 @@
         <v>8</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J62" s="5">
         <v>1</v>
       </c>
       <c r="K62" s="21" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8800,16 +8839,16 @@
         <v>14</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J63" s="2">
         <v>3</v>
       </c>
       <c r="K63" s="22" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8835,19 +8874,19 @@
         <v>15</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J64" s="5">
         <v>37</v>
       </c>
       <c r="K64" s="21" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="24" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -8870,16 +8909,16 @@
         <v>15</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J65" s="2">
         <v>1</v>
       </c>
       <c r="K65" s="22" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="26" x14ac:dyDescent="0.35">
@@ -8908,13 +8947,13 @@
         <v>433</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J66" s="5">
         <v>1</v>
       </c>
       <c r="K66" s="21" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -8943,13 +8982,13 @@
         <v>179</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J67" s="2">
         <v>20</v>
       </c>
       <c r="K67" s="22" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="26" x14ac:dyDescent="0.35">
@@ -8978,7 +9017,7 @@
         <v>433</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="J68" s="5">
         <v>1</v>
@@ -9013,13 +9052,13 @@
         <v>179</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J69" s="2">
         <v>1</v>
       </c>
       <c r="K69" s="22" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="26" x14ac:dyDescent="0.35">
@@ -9048,13 +9087,13 @@
         <v>433</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J70" s="5">
         <v>1</v>
       </c>
       <c r="K70" s="21" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -9083,13 +9122,13 @@
         <v>179</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J71" s="2">
         <v>1</v>
       </c>
       <c r="K71" s="22" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="26" x14ac:dyDescent="0.35">
@@ -9118,13 +9157,13 @@
         <v>433</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J72" s="5">
         <v>1</v>
       </c>
       <c r="K72" s="21" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9150,16 +9189,16 @@
         <v>17</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J73" s="2">
         <v>32</v>
       </c>
       <c r="K73" s="22" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9188,13 +9227,13 @@
         <v>189</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J74" s="5">
         <v>35</v>
       </c>
       <c r="K74" s="21" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9223,13 +9262,13 @@
         <v>189</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="J75" s="2">
         <v>11</v>
       </c>
       <c r="K75" s="22" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9255,16 +9294,16 @@
         <v>17</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J76" s="5">
         <v>1</v>
       </c>
       <c r="K76" s="21" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9293,13 +9332,13 @@
         <v>189</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J77" s="2">
         <v>1</v>
       </c>
       <c r="K77" s="22" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9325,16 +9364,16 @@
         <v>17</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J78" s="5">
         <v>1</v>
       </c>
       <c r="K78" s="21" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9363,13 +9402,13 @@
         <v>189</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="J79" s="2">
         <v>1</v>
       </c>
       <c r="K79" s="22" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9395,16 +9434,16 @@
         <v>18</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J80" s="5">
         <v>5</v>
       </c>
       <c r="K80" s="21" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9433,13 +9472,13 @@
         <v>199</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J81" s="2">
         <v>4</v>
       </c>
       <c r="K81" s="22" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9468,13 +9507,13 @@
         <v>199</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J82" s="5">
         <v>4</v>
       </c>
       <c r="K82" s="21" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9503,13 +9542,13 @@
         <v>202</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="J83" s="2">
         <v>22</v>
       </c>
       <c r="K83" s="22" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9538,13 +9577,13 @@
         <v>202</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J84" s="5">
         <v>11</v>
       </c>
       <c r="K84" s="21" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9573,13 +9612,13 @@
         <v>202</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J85" s="2">
         <v>17</v>
       </c>
       <c r="K85" s="22" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9608,13 +9647,13 @@
         <v>202</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J86" s="5">
         <v>1</v>
       </c>
       <c r="K86" s="21" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9643,13 +9682,13 @@
         <v>202</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J87" s="2">
         <v>1</v>
       </c>
       <c r="K87" s="22" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9678,13 +9717,13 @@
         <v>202</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J88" s="5">
         <v>1</v>
       </c>
       <c r="K88" s="21" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9710,16 +9749,16 @@
         <v>20</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J89" s="2">
         <v>53</v>
       </c>
       <c r="K89" s="22" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9745,16 +9784,16 @@
         <v>11</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J90" s="5">
         <v>16</v>
       </c>
       <c r="K90" s="21" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9780,16 +9819,16 @@
         <v>11</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="J91" s="2">
         <v>19</v>
       </c>
       <c r="K91" s="22" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9815,16 +9854,16 @@
         <v>20</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="J92" s="5">
         <v>1</v>
       </c>
       <c r="K92" s="21" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9850,16 +9889,16 @@
         <v>11</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="J93" s="2">
         <v>1</v>
       </c>
       <c r="K93" s="22" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9885,16 +9924,16 @@
         <v>20</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="J94" s="5">
         <v>1</v>
       </c>
       <c r="K94" s="21" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9920,16 +9959,16 @@
         <v>12</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J95" s="2">
         <v>30</v>
       </c>
       <c r="K95" s="22" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9955,16 +9994,16 @@
         <v>20</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J96" s="5">
         <v>1</v>
       </c>
       <c r="K96" s="21" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -9990,16 +10029,16 @@
         <v>12</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J97" s="2">
         <v>1</v>
       </c>
       <c r="K97" s="22" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
@@ -10048,16 +10087,16 @@
         <v>12</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="J99" s="2">
         <v>1</v>
       </c>
       <c r="K99" s="22" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
@@ -10083,28 +10122,38 @@
       <c r="J100" s="8"/>
       <c r="K100" s="23"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A101" s="8">
+    <row r="101" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A101" s="2">
         <v>100</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C101" s="10" t="s">
+      <c r="C101" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="D101" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="E101" s="17" t="s">
-        <v>448</v>
-      </c>
-      <c r="F101" s="8"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="10"/>
-      <c r="I101" s="10"/>
-      <c r="J101" s="8"/>
-      <c r="K101" s="23"/>
+      <c r="E101" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="G101" s="2">
+        <v>11</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="I101" s="4"/>
+      <c r="J101" s="2">
+        <v>1</v>
+      </c>
+      <c r="K101" s="22" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="102" spans="1:11" ht="26" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
@@ -10129,16 +10178,16 @@
         <v>22</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="J102" s="5">
         <v>11</v>
       </c>
       <c r="K102" s="21" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10164,16 +10213,16 @@
         <v>14</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="J103" s="2">
         <v>30</v>
       </c>
       <c r="K103" s="22" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
@@ -10245,16 +10294,16 @@
         <v>26</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="J106" s="5">
         <v>1</v>
       </c>
       <c r="K106" s="21" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="26" x14ac:dyDescent="0.35">
@@ -10280,16 +10329,16 @@
         <v>13</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="J107" s="2">
         <v>7</v>
       </c>
       <c r="K107" s="22" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="26" x14ac:dyDescent="0.35">
@@ -10315,16 +10364,16 @@
         <v>12</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="J108" s="5">
         <v>7</v>
       </c>
       <c r="K108" s="21" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
@@ -10350,10 +10399,10 @@
         <v>26</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="J109" s="2">
         <v>1</v>
@@ -10388,13 +10437,13 @@
         <v>242</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="J110" s="5">
         <v>3</v>
       </c>
       <c r="K110" s="21" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10423,13 +10472,13 @@
         <v>242</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="J111" s="2">
         <v>3</v>
       </c>
       <c r="K111" s="22" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10455,16 +10504,16 @@
         <v>21</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="J112" s="5">
         <v>4</v>
       </c>
       <c r="K112" s="21" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.35">
@@ -10490,16 +10539,16 @@
         <v>17</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="J113" s="2">
         <v>1</v>
       </c>
       <c r="K113" s="22" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10525,16 +10574,16 @@
         <v>15</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="J114" s="5">
         <v>1</v>
       </c>
       <c r="K114" s="21" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.35">
@@ -10583,16 +10632,16 @@
         <v>25</v>
       </c>
       <c r="H116" s="7" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="J116" s="5">
         <v>4</v>
       </c>
       <c r="K116" s="21" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10621,13 +10670,13 @@
         <v>249</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="J117" s="2">
         <v>3</v>
       </c>
       <c r="K117" s="22" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10656,13 +10705,13 @@
         <v>249</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="J118" s="5">
         <v>2</v>
       </c>
       <c r="K118" s="21" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.35">
@@ -10780,16 +10829,16 @@
         <v>27</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="J123" s="2">
         <v>8</v>
       </c>
       <c r="K123" s="22" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10818,13 +10867,13 @@
         <v>271</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="J124" s="5">
         <v>56</v>
       </c>
       <c r="K124" s="21" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10853,13 +10902,13 @@
         <v>271</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="J125" s="2">
         <v>79</v>
       </c>
       <c r="K125" s="22" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10885,16 +10934,16 @@
         <v>28</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="J126" s="5">
         <v>3</v>
       </c>
       <c r="K126" s="21" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10920,16 +10969,16 @@
         <v>5</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="J127" s="2">
         <v>1</v>
       </c>
       <c r="K127" s="22" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10955,16 +11004,16 @@
         <v>5</v>
       </c>
       <c r="H128" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J128" s="5">
         <v>1</v>
       </c>
       <c r="K128" s="21" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -10990,16 +11039,16 @@
         <v>29</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="J129" s="2">
         <v>2</v>
       </c>
       <c r="K129" s="22" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.35">
@@ -11025,16 +11074,16 @@
         <v>30</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="J130" s="5">
         <v>4</v>
       </c>
       <c r="K130" s="21" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -11060,16 +11109,16 @@
         <v>11</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="J131" s="2">
         <v>1</v>
       </c>
       <c r="K131" s="22" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -11095,16 +11144,16 @@
         <v>11</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="J132" s="5">
         <v>1</v>
       </c>
       <c r="K132" s="21" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -11133,37 +11182,47 @@
         <v>265</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="J133" s="2">
         <v>40</v>
       </c>
       <c r="K133" s="22" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A134" s="8">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A134" s="5">
         <v>133</v>
       </c>
-      <c r="B134" s="9" t="s">
+      <c r="B134" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C134" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="D134" s="8" t="s">
+      <c r="D134" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="E134" s="17" t="s">
-        <v>448</v>
-      </c>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
-      <c r="H134" s="10"/>
-      <c r="I134" s="10"/>
-      <c r="J134" s="8"/>
-      <c r="K134" s="23"/>
+      <c r="E134" s="20" t="s">
+        <v>599</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="G134" s="5">
+        <v>8</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="I134" s="7"/>
+      <c r="J134" s="5">
+        <v>1</v>
+      </c>
+      <c r="K134" s="21" t="s">
+        <v>660</v>
+      </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="8">
@@ -11214,60 +11273,84 @@
         <v>267</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="J136" s="5">
         <v>3</v>
       </c>
       <c r="K136" s="21" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A137" s="8">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="24" x14ac:dyDescent="0.35">
+      <c r="A137" s="2">
         <v>136</v>
       </c>
-      <c r="B137" s="9" t="s">
+      <c r="B137" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C137" s="10" t="s">
+      <c r="C137" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="D137" s="8" t="s">
+      <c r="D137" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="E137" s="17" t="s">
-        <v>448</v>
-      </c>
-      <c r="F137" s="8"/>
-      <c r="G137" s="8"/>
-      <c r="H137" s="10"/>
-      <c r="I137" s="10"/>
-      <c r="J137" s="8"/>
-      <c r="K137" s="23"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A138" s="8">
+      <c r="E137" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="G137" s="2">
+        <v>17</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="J137" s="2">
+        <v>1</v>
+      </c>
+      <c r="K137" s="22" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="24" x14ac:dyDescent="0.35">
+      <c r="A138" s="5">
         <v>137</v>
       </c>
-      <c r="B138" s="9" t="s">
+      <c r="B138" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="C138" s="10" t="s">
+      <c r="C138" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D138" s="8" t="s">
+      <c r="D138" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="E138" s="17" t="s">
-        <v>448</v>
-      </c>
-      <c r="F138" s="8"/>
-      <c r="G138" s="8"/>
-      <c r="H138" s="10"/>
-      <c r="I138" s="10"/>
-      <c r="J138" s="8"/>
-      <c r="K138" s="23"/>
+      <c r="E138" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="G138" s="5">
+        <v>15</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="I138" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="J138" s="5">
+        <v>1</v>
+      </c>
+      <c r="K138" s="21" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="139" spans="1:11" ht="24" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
@@ -11295,13 +11378,13 @@
         <v>269</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="J139" s="2">
         <v>2</v>
       </c>
       <c r="K139" s="22" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.35">
@@ -11373,16 +11456,16 @@
         <v>27</v>
       </c>
       <c r="H142" s="7" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="J142" s="5">
         <v>8</v>
       </c>
       <c r="K142" s="21" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -11411,13 +11494,13 @@
         <v>271</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="J143" s="2">
         <v>56</v>
       </c>
       <c r="K143" s="22" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -11446,13 +11529,13 @@
         <v>271</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="J144" s="5">
         <v>79</v>
       </c>
       <c r="K144" s="21" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.35">
@@ -11502,13 +11585,13 @@
         <v>399</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="J146" s="5">
         <v>1</v>
       </c>
       <c r="K146" s="21" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.35">
@@ -11535,13 +11618,13 @@
         <v>399</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="J147" s="2">
         <v>1</v>
       </c>
       <c r="K147" s="22" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="24" x14ac:dyDescent="0.35">
@@ -11568,13 +11651,13 @@
         <v>399</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="J148" s="5">
         <v>1</v>
       </c>
       <c r="K148" s="21" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.35">
@@ -11603,13 +11686,13 @@
         <v>265</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="J149" s="2">
         <v>1</v>
       </c>
       <c r="K149" s="22" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.35">
@@ -11638,13 +11721,13 @@
         <v>271</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="J150" s="5">
         <v>1</v>
       </c>
       <c r="K150" s="21" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.35">
@@ -11673,13 +11756,13 @@
         <v>271</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="J151" s="2">
         <v>1</v>
       </c>
       <c r="K151" s="22" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.35">
@@ -11706,17 +11789,17 @@
         <v>399</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="J152" s="5">
         <v>1</v>
       </c>
       <c r="K152" s="21" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{97AF4AC5-9F13-4DF0-840B-0C580C166032}"/>
+  <autoFilter ref="A1:K1" xr:uid="{63C22EEF-9522-413E-AD40-ED5C9924E1A2}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>